--- a/data_files/Site glossary.xlsx
+++ b/data_files/Site glossary.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nih.sharepoint.com/sites/NCI-CBIIT-FNLCCDI/Shared Documents/CCDC (Data Catalog nee PODCat)/2-Executing/System Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="13_ncr:1_{CD305CA4-F6E6-494C-8D70-07316997D1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FD66A9E-9FA9-48A2-AE61-7BF4313BE6DF}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="13_ncr:1_{CD305CA4-F6E6-494C-8D70-07316997D1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B74640D5-A2E0-4A20-9BF4-23D0A9324AD6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4110CF64-F05A-4DD9-960E-BC3FCD1C46EE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4110CF64-F05A-4DD9-960E-BC3FCD1C46EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Site glossary" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Site glossary'!$A$1:$Z$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Site glossary'!$A$1:$Z$93</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="289">
   <si>
     <t>Term Category</t>
   </si>
@@ -498,12 +498,6 @@
   </si>
   <si>
     <t>Patient Derived Xenograft</t>
-  </si>
-  <si>
-    <t>PDX-AIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patient-Derived Xenograft and Advanced In Vivo Models </t>
   </si>
   <si>
     <t>PDXNet</t>
@@ -918,7 +912,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1067,9 +1061,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1107,7 +1101,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1213,7 +1207,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1355,7 +1349,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1363,17 +1357,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69208F35-5666-473F-97EF-CB7A96B85984}">
-  <dimension ref="A1:E131"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <dimension ref="A1:E130"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="97.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="97.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1390,7 +1384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1407,7 +1401,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29.1">
+    <row r="3" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1418,7 +1412,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1435,7 +1429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1446,7 +1440,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1457,7 +1451,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1468,7 +1462,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="72.599999999999994">
+    <row r="8" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1485,7 +1479,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1496,7 +1490,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -1507,7 +1501,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1518,7 +1512,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1529,7 +1523,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1540,7 +1534,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1557,7 +1551,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1568,7 +1562,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1579,7 +1573,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1590,7 +1584,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1601,7 +1595,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -1618,7 +1612,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1629,7 +1623,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -1640,7 +1634,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="43.5">
+    <row r="22" spans="1:5" ht="87" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -1651,7 +1645,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -1662,7 +1656,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -1673,7 +1667,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1684,7 +1678,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="57.95">
+    <row r="26" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>68</v>
       </c>
@@ -1695,7 +1689,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -1706,7 +1700,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -1717,7 +1711,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="29.1">
+    <row r="29" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1734,7 +1728,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1745,7 +1739,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -1756,7 +1750,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -1767,7 +1761,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -1778,7 +1772,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -1789,7 +1783,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -1800,7 +1794,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -1811,7 +1805,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -1822,7 +1816,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -1833,7 +1827,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1844,7 +1838,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -1855,7 +1849,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -1866,7 +1860,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="29.1">
+    <row r="42" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -1883,7 +1877,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -1894,7 +1888,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -1905,7 +1899,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="43.5">
+    <row r="45" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>10</v>
       </c>
@@ -1922,7 +1916,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -1933,7 +1927,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -1944,7 +1938,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>116</v>
       </c>
@@ -1955,7 +1949,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -1966,7 +1960,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -1977,7 +1971,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -1988,7 +1982,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>17</v>
       </c>
@@ -1999,7 +1993,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>17</v>
       </c>
@@ -2010,7 +2004,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -2021,7 +2015,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>20</v>
       </c>
@@ -2032,7 +2026,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -2043,7 +2037,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -2054,7 +2048,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>20</v>
       </c>
@@ -2065,7 +2059,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -2076,7 +2070,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -2087,7 +2081,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -2098,7 +2092,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2109,7 +2103,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -2120,7 +2114,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -2131,7 +2125,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>20</v>
       </c>
@@ -2142,7 +2136,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -2153,31 +2147,31 @@
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>17</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="5" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>17</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" t="s">
         <v>157</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="B69" t="s">
         <v>159</v>
@@ -2186,9 +2180,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
         <v>161</v>
@@ -2197,7 +2191,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -2208,86 +2202,86 @@
         <v>164</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" ht="87" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>5</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="43.5">
+    <row r="73" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>167</v>
       </c>
       <c r="B73" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="43.5">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B74" t="s">
         <v>170</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="29.1">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="B75" t="s">
         <v>172</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>61</v>
+        <v>165</v>
       </c>
       <c r="B76" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C76" t="s">
+    </row>
+    <row r="77" spans="1:5" ht="145" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>10</v>
+      </c>
+      <c r="B77" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" ht="29.1">
-      <c r="A77" t="s">
-        <v>167</v>
-      </c>
-      <c r="B77" t="s">
-        <v>3</v>
-      </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="10" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="72.599999999999994">
+    <row r="78" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>10</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" t="s">
         <v>177</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C78" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="72.599999999999994">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="B79" t="s">
         <v>179</v>
@@ -2295,47 +2289,47 @@
       <c r="C79" s="1" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="80" spans="1:5">
+      <c r="D79" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>167</v>
-      </c>
-      <c r="B80" t="s">
-        <v>181</v>
-      </c>
-      <c r="C80" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D80" t="s">
-        <v>8</v>
-      </c>
-      <c r="E80" t="s">
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>17</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" ht="29.1">
-      <c r="A81" t="s">
-        <v>68</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="10" t="s">
+      <c r="C81" s="5" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>17</v>
-      </c>
-      <c r="B82" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B82" t="s">
         <v>185</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>61</v>
       </c>
@@ -2346,57 +2340,57 @@
         <v>188</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" ht="116" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="B84" t="s">
         <v>189</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="1" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" ht="57.95">
+      <c r="D84" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="B85" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D85" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>61</v>
-      </c>
-      <c r="B86" t="s">
+        <v>17</v>
+      </c>
+      <c r="B86" s="5" t="s">
         <v>194</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>17</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" t="s">
         <v>196</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>17</v>
       </c>
@@ -2407,7 +2401,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>17</v>
       </c>
@@ -2418,7 +2412,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>17</v>
       </c>
@@ -2429,7 +2423,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>17</v>
       </c>
@@ -2440,129 +2434,129 @@
         <v>205</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>17</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="5" t="s">
         <v>206</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>17</v>
-      </c>
-      <c r="B93" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B93" t="s">
         <v>208</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="B94" t="s">
         <v>210</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>20</v>
-      </c>
-      <c r="B95" t="s">
+        <v>17</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>212</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>17</v>
-      </c>
-      <c r="B96" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B96" t="s">
         <v>214</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="B97" t="s">
         <v>216</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="9" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="D97" t="s">
+        <v>15</v>
+      </c>
+      <c r="E97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B98" t="s">
-        <v>218</v>
-      </c>
-      <c r="C98" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="D98" t="s">
+      <c r="C98" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>221</v>
+      </c>
+      <c r="B99" t="s">
+        <v>222</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D99" t="s">
         <v>15</v>
       </c>
-      <c r="E98" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="29.1">
-      <c r="A99" t="s">
-        <v>51</v>
-      </c>
-      <c r="B99" t="s">
-        <v>221</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="72.599999999999994">
+      <c r="E99" s="11" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>223</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>224</v>
-      </c>
-      <c r="C100" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D100" t="s">
-        <v>15</v>
-      </c>
-      <c r="E100" s="11" t="s">
+      <c r="C100" s="8" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>17</v>
       </c>
       <c r="B101" t="s">
         <v>227</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="C101" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -2573,9 +2567,9 @@
         <v>230</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B103" t="s">
         <v>231</v>
@@ -2584,9 +2578,9 @@
         <v>232</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
         <v>233</v>
@@ -2595,7 +2589,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>17</v>
       </c>
@@ -2606,9 +2600,9 @@
         <v>236</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="B106" t="s">
         <v>237</v>
@@ -2616,42 +2610,42 @@
       <c r="C106" s="1" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" ht="29.1">
+      <c r="D106" t="s">
+        <v>15</v>
+      </c>
+      <c r="E106" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="B107" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D107" t="s">
         <v>15</v>
       </c>
       <c r="E107" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="72.599999999999994">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D108" t="s">
-        <v>15</v>
-      </c>
-      <c r="E108" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>17</v>
       </c>
@@ -2662,7 +2656,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -2673,7 +2667,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>17</v>
       </c>
@@ -2684,7 +2678,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>17</v>
       </c>
@@ -2695,7 +2689,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>17</v>
       </c>
@@ -2706,7 +2700,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>17</v>
       </c>
@@ -2717,7 +2711,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>17</v>
       </c>
@@ -2728,7 +2722,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>17</v>
       </c>
@@ -2739,7 +2733,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>17</v>
       </c>
@@ -2750,7 +2744,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>17</v>
       </c>
@@ -2761,7 +2755,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>17</v>
       </c>
@@ -2772,7 +2766,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>17</v>
       </c>
@@ -2783,7 +2777,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>17</v>
       </c>
@@ -2794,51 +2788,51 @@
         <v>270</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>17</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="12" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>17</v>
       </c>
-      <c r="B123" s="12" t="s">
+      <c r="B123" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="C123" s="12" t="s">
+      <c r="C123" s="13" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>17</v>
       </c>
-      <c r="B124" s="13" t="s">
+      <c r="B124" t="s">
         <v>275</v>
       </c>
-      <c r="C124" s="13" t="s">
+      <c r="C124" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>17</v>
       </c>
       <c r="B125" t="s">
         <v>277</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>17</v>
       </c>
@@ -2849,7 +2843,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>17</v>
       </c>
@@ -2860,7 +2854,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>17</v>
       </c>
@@ -2871,7 +2865,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>17</v>
       </c>
@@ -2882,36 +2876,25 @@
         <v>286</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>17</v>
       </c>
       <c r="B130" t="s">
         <v>287</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" s="14" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="15">
-      <c r="A131" t="s">
-        <v>17</v>
-      </c>
-      <c r="B131" t="s">
-        <v>289</v>
-      </c>
-      <c r="C131" s="14" t="s">
-        <v>290</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Z94" xr:uid="{A4DAB4A1-0C2C-4B2F-A024-FF4C6E1E16D8}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E98">
-      <sortCondition ref="B1:B94"/>
+  <autoFilter ref="A1:Z93" xr:uid="{A4DAB4A1-0C2C-4B2F-A024-FF4C6E1E16D8}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E97">
+      <sortCondition ref="B1:B93"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="E100" r:id="rId1" xr:uid="{D3DBCC56-4DE9-4D48-A14F-C1E905DF0FDE}"/>
+    <hyperlink ref="E99" r:id="rId1" xr:uid="{D3DBCC56-4DE9-4D48-A14F-C1E905DF0FDE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
@@ -2919,15 +2902,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002BAA57F805DE4D498A43031B16C0C8A1" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d169cae7b697a38c1f2a3ff7bc83911">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="00850a8a-55a0-4f29-bb56-d3de9b9bc75c" xmlns:ns3="33e70369-3675-4c3b-99e1-030eb9633bdf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3d7b88af5274db58a2019a9f8258b200" ns2:_="" ns3:_="">
     <xsd:import namespace="00850a8a-55a0-4f29-bb56-d3de9b9bc75c"/>
@@ -3174,6 +3148,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3186,13 +3169,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7554B1E-EA5B-4036-8BEB-CEB54DFFA990}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{408CD603-C2F6-45F8-91C0-1EC5F05A3CA2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="00850a8a-55a0-4f29-bb56-d3de9b9bc75c"/>
+    <ds:schemaRef ds:uri="33e70369-3675-4c3b-99e1-030eb9633bdf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{408CD603-C2F6-45F8-91C0-1EC5F05A3CA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7554B1E-EA5B-4036-8BEB-CEB54DFFA990}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13521947-7B63-4043-9A52-D2F3EDCA31C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13521947-7B63-4043-9A52-D2F3EDCA31C1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="33e70369-3675-4c3b-99e1-030eb9633bdf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="00850a8a-55a0-4f29-bb56-d3de9b9bc75c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data_files/Site glossary.xlsx
+++ b/data_files/Site glossary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nih.sharepoint.com/sites/NCI-CBIIT-FNLCCDI/Shared Documents/CCDC (Data Catalog nee PODCat)/2-Executing/System Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="13_ncr:1_{CD305CA4-F6E6-494C-8D70-07316997D1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B74640D5-A2E0-4A20-9BF4-23D0A9324AD6}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{CD305CA4-F6E6-494C-8D70-07316997D1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90C75E1B-174C-4937-9867-F59B97C3FF63}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4110CF64-F05A-4DD9-960E-BC3FCD1C46EE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4110CF64-F05A-4DD9-960E-BC3FCD1C46EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Site glossary" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="299">
   <si>
     <t>Term Category</t>
   </si>
@@ -185,9 +185,6 @@
     <t>CIViC</t>
   </si>
   <si>
-    <t>Clinical Interpretations of Variants in Cancer</t>
-  </si>
-  <si>
     <t>CLIA</t>
   </si>
   <si>
@@ -905,14 +902,47 @@
     <t>NF-OSI</t>
   </si>
   <si>
-    <t>NF Data Portal</t>
+    <t>caDSR</t>
+  </si>
+  <si>
+    <t>Cancer Data Standards Registry and Repository</t>
+  </si>
+  <si>
+    <t>FrESCO</t>
+  </si>
+  <si>
+    <t>Framework for Exploring Scalable Computational Oncology</t>
+  </si>
+  <si>
+    <t>PMTL</t>
+  </si>
+  <si>
+    <t>Pediatric Molecular Target Lists</t>
+  </si>
+  <si>
+    <t>STQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spatial Transcriptomics Quantification </t>
+  </si>
+  <si>
+    <t>Batch-processing Abstraction for Raw Data Integration</t>
+  </si>
+  <si>
+    <t>BARDI</t>
+  </si>
+  <si>
+    <t>Clinical Interpretation of Variants in Cancer</t>
+  </si>
+  <si>
+    <t>Neurofibromatosis Data Portal Open Science Initiative</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -960,6 +990,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -969,7 +1006,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1005,12 +1042,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF4472C4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4472C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1042,6 +1094,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1357,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69208F35-5666-473F-97EF-CB7A96B85984}">
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36.453125" bestFit="1" customWidth="1"/>
@@ -1581,7 +1634,7 @@
         <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>48</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1589,27 +1642,27 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
         <v>51</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="D19" t="s">
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1617,10 +1670,10 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -1628,10 +1681,10 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="87" x14ac:dyDescent="0.35">
@@ -1639,21 +1692,21 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
         <v>61</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -1661,32 +1714,32 @@
         <v>17</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -1694,10 +1747,10 @@
         <v>17</v>
       </c>
       <c r="B27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -1705,10 +1758,10 @@
         <v>17</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
@@ -1716,27 +1769,27 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="D29" t="s">
         <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" t="s">
         <v>77</v>
-      </c>
-      <c r="C30" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -1744,10 +1797,10 @@
         <v>17</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -1755,10 +1808,10 @@
         <v>20</v>
       </c>
       <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -1766,10 +1819,10 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -1777,10 +1830,10 @@
         <v>17</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -1788,10 +1841,10 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -1799,21 +1852,21 @@
         <v>17</v>
       </c>
       <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -1821,10 +1874,10 @@
         <v>17</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -1832,10 +1885,10 @@
         <v>17</v>
       </c>
       <c r="B39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -1843,10 +1896,10 @@
         <v>17</v>
       </c>
       <c r="B40" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -1854,27 +1907,27 @@
         <v>17</v>
       </c>
       <c r="B41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="D42" t="s">
         <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -1882,10 +1935,10 @@
         <v>17</v>
       </c>
       <c r="B43" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -1893,10 +1946,10 @@
         <v>17</v>
       </c>
       <c r="B44" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
@@ -1904,16 +1957,16 @@
         <v>10</v>
       </c>
       <c r="B45" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" t="s">
         <v>109</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>110</v>
-      </c>
-      <c r="E45" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -1921,10 +1974,10 @@
         <v>17</v>
       </c>
       <c r="B46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" t="s">
         <v>112</v>
-      </c>
-      <c r="C46" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -1932,21 +1985,21 @@
         <v>17</v>
       </c>
       <c r="B47" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" t="s">
         <v>116</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
@@ -1954,21 +2007,21 @@
         <v>17</v>
       </c>
       <c r="B49" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B50" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50" t="s">
         <v>121</v>
-      </c>
-      <c r="C50" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
@@ -1976,10 +2029,10 @@
         <v>17</v>
       </c>
       <c r="B51" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
@@ -1987,10 +2040,10 @@
         <v>17</v>
       </c>
       <c r="B52" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
@@ -1998,10 +2051,10 @@
         <v>17</v>
       </c>
       <c r="B53" t="s">
+        <v>126</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
@@ -2009,10 +2062,10 @@
         <v>17</v>
       </c>
       <c r="B54" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
@@ -2020,10 +2073,10 @@
         <v>20</v>
       </c>
       <c r="B55" t="s">
+        <v>130</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -2031,21 +2084,21 @@
         <v>20</v>
       </c>
       <c r="B56" t="s">
+        <v>132</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B57" t="s">
+        <v>134</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -2053,10 +2106,10 @@
         <v>20</v>
       </c>
       <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
@@ -2064,10 +2117,10 @@
         <v>17</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
@@ -2075,21 +2128,21 @@
         <v>17</v>
       </c>
       <c r="B60" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>142</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
@@ -2097,10 +2150,10 @@
         <v>17</v>
       </c>
       <c r="B62" t="s">
+        <v>144</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
@@ -2108,10 +2161,10 @@
         <v>17</v>
       </c>
       <c r="B63" t="s">
+        <v>146</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
@@ -2119,10 +2172,10 @@
         <v>17</v>
       </c>
       <c r="B64" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
@@ -2130,10 +2183,10 @@
         <v>20</v>
       </c>
       <c r="B65" t="s">
+        <v>150</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
@@ -2141,10 +2194,10 @@
         <v>17</v>
       </c>
       <c r="B66" t="s">
+        <v>152</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -2152,10 +2205,10 @@
         <v>17</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -2163,21 +2216,21 @@
         <v>17</v>
       </c>
       <c r="B68" t="s">
+        <v>156</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B69" t="s">
+        <v>158</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -2185,10 +2238,10 @@
         <v>17</v>
       </c>
       <c r="B70" t="s">
+        <v>160</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -2196,65 +2249,65 @@
         <v>17</v>
       </c>
       <c r="B71" t="s">
+        <v>162</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="87" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B72" t="s">
         <v>5</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" t="s">
         <v>167</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B74" t="s">
+        <v>169</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B75" t="s">
+        <v>171</v>
+      </c>
+      <c r="C75" t="s">
         <v>172</v>
-      </c>
-      <c r="C75" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B76" t="s">
         <v>3</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="145" x14ac:dyDescent="0.35">
@@ -2262,10 +2315,10 @@
         <v>10</v>
       </c>
       <c r="B77" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C77" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
@@ -2273,38 +2326,38 @@
         <v>10</v>
       </c>
       <c r="B78" t="s">
+        <v>176</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B79" t="s">
+        <v>178</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="D79" t="s">
         <v>8</v>
       </c>
       <c r="E79" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
@@ -2312,32 +2365,32 @@
         <v>17</v>
       </c>
       <c r="B81" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B82" t="s">
+        <v>184</v>
+      </c>
+      <c r="C82" t="s">
         <v>185</v>
-      </c>
-      <c r="C82" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B83" t="s">
+        <v>186</v>
+      </c>
+      <c r="C83" t="s">
         <v>187</v>
-      </c>
-      <c r="C83" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="116" x14ac:dyDescent="0.35">
@@ -2345,27 +2398,27 @@
         <v>5</v>
       </c>
       <c r="B84" t="s">
+        <v>188</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="D84" t="s">
         <v>8</v>
       </c>
       <c r="E84" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B85" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
@@ -2373,10 +2426,10 @@
         <v>17</v>
       </c>
       <c r="B86" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
@@ -2384,10 +2437,10 @@
         <v>17</v>
       </c>
       <c r="B87" t="s">
+        <v>195</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
@@ -2395,10 +2448,10 @@
         <v>17</v>
       </c>
       <c r="B88" t="s">
+        <v>197</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="29" x14ac:dyDescent="0.35">
@@ -2406,10 +2459,10 @@
         <v>17</v>
       </c>
       <c r="B89" t="s">
+        <v>199</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
@@ -2417,10 +2470,10 @@
         <v>17</v>
       </c>
       <c r="B90" t="s">
+        <v>201</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
@@ -2428,10 +2481,10 @@
         <v>17</v>
       </c>
       <c r="B91" t="s">
+        <v>203</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
@@ -2439,21 +2492,21 @@
         <v>17</v>
       </c>
       <c r="B92" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B93" t="s">
+        <v>207</v>
+      </c>
+      <c r="C93" t="s">
         <v>208</v>
-      </c>
-      <c r="C93" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
@@ -2461,10 +2514,10 @@
         <v>20</v>
       </c>
       <c r="B94" t="s">
+        <v>209</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
@@ -2472,21 +2525,21 @@
         <v>17</v>
       </c>
       <c r="B95" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B96" t="s">
+        <v>213</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="29" x14ac:dyDescent="0.35">
@@ -2494,44 +2547,44 @@
         <v>39</v>
       </c>
       <c r="B97" t="s">
+        <v>215</v>
+      </c>
+      <c r="C97" s="9" t="s">
         <v>216</v>
-      </c>
-      <c r="C97" s="9" t="s">
-        <v>217</v>
       </c>
       <c r="D97" t="s">
         <v>15</v>
       </c>
       <c r="E97" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B98" t="s">
+        <v>218</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
+        <v>220</v>
+      </c>
+      <c r="B99" t="s">
         <v>221</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="D99" t="s">
         <v>15</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
@@ -2539,10 +2592,10 @@
         <v>17</v>
       </c>
       <c r="B100" t="s">
+        <v>224</v>
+      </c>
+      <c r="C100" s="8" t="s">
         <v>225</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
@@ -2550,10 +2603,10 @@
         <v>17</v>
       </c>
       <c r="B101" t="s">
+        <v>226</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
@@ -2561,10 +2614,10 @@
         <v>17</v>
       </c>
       <c r="B102" t="s">
+        <v>228</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
@@ -2572,10 +2625,10 @@
         <v>20</v>
       </c>
       <c r="B103" t="s">
+        <v>230</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
@@ -2583,10 +2636,10 @@
         <v>17</v>
       </c>
       <c r="B104" t="s">
+        <v>232</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
@@ -2594,27 +2647,27 @@
         <v>17</v>
       </c>
       <c r="B105" t="s">
+        <v>234</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B106" t="s">
+        <v>236</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="D106" t="s">
         <v>15</v>
       </c>
       <c r="E106" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
@@ -2622,16 +2675,16 @@
         <v>10</v>
       </c>
       <c r="B107" t="s">
+        <v>239</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="D107" t="s">
         <v>15</v>
       </c>
       <c r="E107" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
@@ -2639,10 +2692,10 @@
         <v>17</v>
       </c>
       <c r="B108" t="s">
+        <v>242</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
@@ -2650,10 +2703,10 @@
         <v>17</v>
       </c>
       <c r="B109" t="s">
+        <v>244</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
@@ -2661,10 +2714,10 @@
         <v>17</v>
       </c>
       <c r="B110" t="s">
+        <v>246</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
@@ -2672,10 +2725,10 @@
         <v>17</v>
       </c>
       <c r="B111" t="s">
+        <v>248</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
@@ -2683,10 +2736,10 @@
         <v>17</v>
       </c>
       <c r="B112" t="s">
+        <v>250</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
@@ -2694,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="B113" t="s">
+        <v>252</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="29" x14ac:dyDescent="0.35">
@@ -2705,10 +2758,10 @@
         <v>17</v>
       </c>
       <c r="B114" t="s">
+        <v>254</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
@@ -2716,10 +2769,10 @@
         <v>17</v>
       </c>
       <c r="B115" t="s">
+        <v>256</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
@@ -2727,10 +2780,10 @@
         <v>17</v>
       </c>
       <c r="B116" t="s">
+        <v>258</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
@@ -2738,10 +2791,10 @@
         <v>17</v>
       </c>
       <c r="B117" t="s">
+        <v>260</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
@@ -2749,10 +2802,10 @@
         <v>17</v>
       </c>
       <c r="B118" t="s">
+        <v>262</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
@@ -2760,10 +2813,10 @@
         <v>17</v>
       </c>
       <c r="B119" t="s">
+        <v>264</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
@@ -2771,10 +2824,10 @@
         <v>17</v>
       </c>
       <c r="B120" t="s">
+        <v>266</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
@@ -2782,10 +2835,10 @@
         <v>17</v>
       </c>
       <c r="B121" t="s">
+        <v>268</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
@@ -2793,10 +2846,10 @@
         <v>17</v>
       </c>
       <c r="B122" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="C122" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="C122" s="12" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
@@ -2804,10 +2857,10 @@
         <v>17</v>
       </c>
       <c r="B123" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="C123" s="13" t="s">
         <v>273</v>
-      </c>
-      <c r="C123" s="13" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
@@ -2815,10 +2868,10 @@
         <v>17</v>
       </c>
       <c r="B124" t="s">
+        <v>274</v>
+      </c>
+      <c r="C124" t="s">
         <v>275</v>
-      </c>
-      <c r="C124" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
@@ -2826,10 +2879,10 @@
         <v>17</v>
       </c>
       <c r="B125" t="s">
+        <v>276</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
@@ -2837,10 +2890,10 @@
         <v>17</v>
       </c>
       <c r="B126" t="s">
+        <v>278</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
@@ -2848,10 +2901,10 @@
         <v>17</v>
       </c>
       <c r="B127" t="s">
+        <v>280</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
@@ -2859,10 +2912,10 @@
         <v>17</v>
       </c>
       <c r="B128" t="s">
+        <v>282</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
@@ -2870,10 +2923,10 @@
         <v>17</v>
       </c>
       <c r="B129" t="s">
+        <v>284</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
@@ -2881,10 +2934,65 @@
         <v>17</v>
       </c>
       <c r="B130" t="s">
+        <v>286</v>
+      </c>
+      <c r="C130" s="14" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>17</v>
+      </c>
+      <c r="B131" t="s">
         <v>287</v>
       </c>
-      <c r="C130" s="14" t="s">
+      <c r="C131" s="15" t="s">
         <v>288</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>17</v>
+      </c>
+      <c r="B132" t="s">
+        <v>289</v>
+      </c>
+      <c r="C132" s="15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>17</v>
+      </c>
+      <c r="B133" t="s">
+        <v>291</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>17</v>
+      </c>
+      <c r="B134" t="s">
+        <v>293</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>17</v>
+      </c>
+      <c r="B135" t="s">
+        <v>296</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -3149,15 +3257,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="00850a8a-55a0-4f29-bb56-d3de9b9bc75c">
@@ -3166,6 +3265,15 @@
     <TaxCatchAll xmlns="33e70369-3675-4c3b-99e1-030eb9633bdf" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3188,26 +3296,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13521947-7B63-4043-9A52-D2F3EDCA31C1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="33e70369-3675-4c3b-99e1-030eb9633bdf"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="00850a8a-55a0-4f29-bb56-d3de9b9bc75c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7554B1E-EA5B-4036-8BEB-CEB54DFFA990}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13521947-7B63-4043-9A52-D2F3EDCA31C1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="33e70369-3675-4c3b-99e1-030eb9633bdf"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="00850a8a-55a0-4f29-bb56-d3de9b9bc75c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data_files/Site glossary.xlsx
+++ b/data_files/Site glossary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nih.sharepoint.com/sites/NCI-CBIIT-FNLCCDI/Shared Documents/CCDC (Data Catalog nee PODCat)/2-Executing/System Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{CD305CA4-F6E6-494C-8D70-07316997D1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90C75E1B-174C-4937-9867-F59B97C3FF63}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C99F1ED5-8264-41A5-AC81-7A1F4A4EB0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4110CF64-F05A-4DD9-960E-BC3FCD1C46EE}"/>
   </bookViews>
@@ -56,6 +56,15 @@
     <t>Reference URL]</t>
   </si>
   <si>
+    <t>Resource Abbreviation</t>
+  </si>
+  <si>
+    <t>ACCIS</t>
+  </si>
+  <si>
+    <t>Automated Childhood Cancer Information System</t>
+  </si>
+  <si>
     <t>Primary Dataset Scope</t>
   </si>
   <si>
@@ -92,7 +101,10 @@
     <t>https://www.cancer.gov/publications/dictionaries/cancer-terms/def/assay</t>
   </si>
   <si>
-    <t>Resource Abbreviation</t>
+    <t>BARDI</t>
+  </si>
+  <si>
+    <t>Batch-processing Abstraction for Raw Data Integration</t>
   </si>
   <si>
     <t>BASIC3</t>
@@ -101,6 +113,45 @@
     <t>Baylor College of Medicine Advancing Sequencing in Childhood Cancer Care</t>
   </si>
   <si>
+    <t>Biorepository</t>
+  </si>
+  <si>
+    <t>A biorepository is a facility that acts as a library for biospecimens, allowing the biospecimens to be available for use in future research. A biospecimen may be from people, animals, or other living organisms. A biorepository will be involved in collecting, cataloguing, and storing biospecimens. The biorepository will also be involved in managing access to and distributing biospecimens to researchers. Some biorepositories store medical information associated with biospecimens.</t>
+  </si>
+  <si>
+    <t>https://toolkit.ncats.nih.gov/glossary/biorepository/</t>
+  </si>
+  <si>
+    <t>Data Content Type</t>
+  </si>
+  <si>
+    <t>Biospecimen</t>
+  </si>
+  <si>
+    <t>A sample of material, such as urine, blood, tissue, cells, DNA, RNA, or protein, from humans, animals, or plants. Biospecimens may be used for a laboratory test or stored in a biorepository to be used for research.</t>
+  </si>
+  <si>
+    <t>https://www.cancer.gov/publications/dictionaries/cancer-terms/def/biospecimen</t>
+  </si>
+  <si>
+    <t>BPC</t>
+  </si>
+  <si>
+    <t>The Biopathology Center</t>
+  </si>
+  <si>
+    <t>BTB</t>
+  </si>
+  <si>
+    <t>Swedish Childhood Tumor Biobank (Barntumörbanken)</t>
+  </si>
+  <si>
+    <t>caDSR</t>
+  </si>
+  <si>
+    <t>Cancer Data Standards Registry and Repository</t>
+  </si>
+  <si>
     <t>General Abbreviation</t>
   </si>
   <si>
@@ -158,6 +209,12 @@
     <t>Centers for Disease Control and Prevention</t>
   </si>
   <si>
+    <t>CEDCD</t>
+  </si>
+  <si>
+    <t>Cancer Epidemiology Descriptive Cohort Database</t>
+  </si>
+  <si>
     <t>Data Content Type, Primary Dataset Scope</t>
   </si>
   <si>
@@ -182,18 +239,24 @@
     <t>Cancer Genome Characterization Initiative</t>
   </si>
   <si>
+    <t>CHoP</t>
+  </si>
+  <si>
+    <t>Children's Hospital of Philadelphia</t>
+  </si>
+  <si>
     <t>CIViC</t>
   </si>
   <si>
+    <t>Clinical Interpretation of Variants in Cancer</t>
+  </si>
+  <si>
     <t>CLIA</t>
   </si>
   <si>
     <t>Clinical Laboratory Improvement Amendments</t>
   </si>
   <si>
-    <t>Data Content Type</t>
-  </si>
-  <si>
     <t>Clinical</t>
   </si>
   <si>
@@ -230,6 +293,12 @@
     <t>Computed Radiography</t>
   </si>
   <si>
+    <t>CRI iAtlas</t>
+  </si>
+  <si>
+    <t>Cancer Research Institute iAtlas</t>
+  </si>
+  <si>
     <t>CSER</t>
   </si>
   <si>
@@ -248,12 +317,30 @@
     <t>A classification of the type of the data hosted in the data resource’s own repository and which corresponds to the research purpose the data serves or from what part of the research process the data were generated.</t>
   </si>
   <si>
+    <t>Data Repository</t>
+  </si>
+  <si>
+    <t>Biomedical data repositories store, organize, validate, archive, preserve, and distribute data, in compliance with the FAIR Data Principles. It is a system for storing multiple research artifacts, provided at least some of the research artifacts contain Individual Research Data. A data repository often contains artifacts from multiple studies. Some data repositories accept research datasets irrespective of the structure of those datasets; other data repositories require all research datasets to conform to a standard reference model.</t>
+  </si>
+  <si>
     <t>dbGaP</t>
   </si>
   <si>
     <t>The database of genotypes and phenotypes</t>
   </si>
   <si>
+    <t>DCEG</t>
+  </si>
+  <si>
+    <t>Division of Cancer Epidemiology &amp; Genetics</t>
+  </si>
+  <si>
+    <t>DepMap</t>
+  </si>
+  <si>
+    <t>Dependency Map</t>
+  </si>
+  <si>
     <t>DIPG</t>
   </si>
   <si>
@@ -275,6 +362,18 @@
     <t>Digital Radiography</t>
   </si>
   <si>
+    <t>ecDNA</t>
+  </si>
+  <si>
+    <t>Circular Extrachromosomal DNA</t>
+  </si>
+  <si>
+    <t>Epidemiologic</t>
+  </si>
+  <si>
+    <t>Relating to the study of the distribution and determinants of health-related states or events (including disease) in populations, and the application of this study to the control of diseases and other health problems.</t>
+  </si>
+  <si>
     <t>ES</t>
   </si>
   <si>
@@ -287,6 +386,12 @@
     <t>Findable, Accessible, Interoperable, and Reusable</t>
   </si>
   <si>
+    <t>FAPTP</t>
+  </si>
+  <si>
+    <t>Florida Association of Pediatric Tumor Programs</t>
+  </si>
+  <si>
     <t>FDA</t>
   </si>
   <si>
@@ -305,12 +410,24 @@
     <t>Freedom of Information Act</t>
   </si>
   <si>
+    <t>FrESCO</t>
+  </si>
+  <si>
+    <t>Framework for Exploring Scalable Computational Oncology</t>
+  </si>
+  <si>
     <t>GDC</t>
   </si>
   <si>
     <t>Genomic Data Commons</t>
   </si>
   <si>
+    <t>GENIE</t>
+  </si>
+  <si>
+    <t>Genomics Evidence Neoplasia Information Exchange</t>
+  </si>
+  <si>
     <t>Genomics/Omics</t>
   </si>
   <si>
@@ -335,12 +452,30 @@
     <t>Human Tumor Atlas Network</t>
   </si>
   <si>
+    <t>IARC</t>
+  </si>
+  <si>
+    <t>International Agency for Research on Cancer</t>
+  </si>
+  <si>
     <t>iCat</t>
   </si>
   <si>
     <t>Individualized Cancer Therapy Study</t>
   </si>
   <si>
+    <t>IDC</t>
+  </si>
+  <si>
+    <t>Imaging Data Commons</t>
+  </si>
+  <si>
+    <t>IICC</t>
+  </si>
+  <si>
+    <t>International Incidence of Childhood Cancer</t>
+  </si>
+  <si>
     <t>Imaging</t>
   </si>
   <si>
@@ -350,6 +485,12 @@
     <t>https://www.cancer.gov/publications/dictionaries/cancer-terms/def/imaging</t>
   </si>
   <si>
+    <t>ITCC P4</t>
+  </si>
+  <si>
+    <t>Innovative Therapies for Children with Cancer Paediatric Preclinical Proof-of-Concept Platform</t>
+  </si>
+  <si>
     <t>JAX</t>
   </si>
   <si>
@@ -371,7 +512,7 @@
     <t>NIH ODSS</t>
   </si>
   <si>
-    <t>https://datascience.nih.gov/biomedical-data-repositories-and-knowledgebases</t>
+    <t>https://datascience.nih.gov/data-ecosystem/biomedical-data-repositories-and-knowledgebases</t>
   </si>
   <si>
     <t>M3Cs</t>
@@ -425,6 +566,12 @@
     <t>My Pediatric and Adult Rare Tumor network</t>
   </si>
   <si>
+    <t>NCCB</t>
+  </si>
+  <si>
+    <t>Norwegian Childhood Cancer Biobank</t>
+  </si>
+  <si>
     <t>NCCR</t>
   </si>
   <si>
@@ -437,6 +584,24 @@
     <t>National Cancer Institute</t>
   </si>
   <si>
+    <t>NCTN</t>
+  </si>
+  <si>
+    <t>National Clinical Trials Network</t>
+  </si>
+  <si>
+    <t>NF-OSI</t>
+  </si>
+  <si>
+    <t>Neurofibromatosis Data Portal Open Science Initiative</t>
+  </si>
+  <si>
+    <t>NICD</t>
+  </si>
+  <si>
+    <t>National Institute for Communicable Diseases</t>
+  </si>
+  <si>
     <t>NIH</t>
   </si>
   <si>
@@ -449,6 +614,12 @@
     <t>Nuclear Medicine</t>
   </si>
   <si>
+    <t>NORDCAN</t>
+  </si>
+  <si>
+    <t>Association of the Nordic Cancer Registries</t>
+  </si>
+  <si>
     <t>NPCR</t>
   </si>
   <si>
@@ -467,6 +638,12 @@
     <t>Oregon Health &amp; Science University</t>
   </si>
   <si>
+    <t>OSE</t>
+  </si>
+  <si>
+    <t>Osteosarcoma Explorer</t>
+  </si>
+  <si>
     <t>OT</t>
   </si>
   <si>
@@ -503,6 +680,12 @@
     <t>PDX Development and Trial Centers Research Network</t>
   </si>
   <si>
+    <t>PeCan</t>
+  </si>
+  <si>
+    <t>Pediatric Cancer Knowledge Base</t>
+  </si>
+  <si>
     <t>PedBrain</t>
   </si>
   <si>
@@ -527,18 +710,48 @@
     <t>Pediatric Molecular Analysis for Therapy Choice</t>
   </si>
   <si>
+    <t>PIVOT</t>
+  </si>
+  <si>
+    <t>Pediatric Preclinical In Vivo Testing Consortium</t>
+  </si>
+  <si>
+    <t>PMTL</t>
+  </si>
+  <si>
+    <t>Pediatric Molecular Target Lists</t>
+  </si>
+  <si>
     <t>PPTC</t>
   </si>
   <si>
     <t>Pediatric Preclinical Testing Consortium</t>
   </si>
   <si>
+    <t>PPTP</t>
+  </si>
+  <si>
+    <t>Pediatric Preclinical Testing Program</t>
+  </si>
+  <si>
     <t>Dataset Structure</t>
   </si>
   <si>
     <t>A classification of common administrative or physical construct to which a researcher associates data. For example, a dataset whose scope is a project contains information belonging to one project. A typical dataset scope is Project, Program, or Collection. Collection is a generic scope whose scoping criteria are not built into the term.</t>
   </si>
   <si>
+    <t>Data Element</t>
+  </si>
+  <si>
+    <t>Proband</t>
+  </si>
+  <si>
+    <t>A proband is a person in a family to receive genetic counseling and/or testing for a suspected hereditary risk or diagnosed disease. A proband may or may not be affected with the disease in question. If the value is true, then the case subject may have been diagnosed with the disease under studied. If the value is false, then the case subject is a member of the family of a proband study participant. The proband indicator for the case carries over to a sample taken from a case subject.</t>
+  </si>
+  <si>
+    <t>https://www.cancer.gov/publications/dictionaries/genetics-dictionary/def/proband</t>
+  </si>
+  <si>
     <t>Primary Dataset Scope, Resource Type</t>
   </si>
   <si>
@@ -554,6 +767,12 @@
     <t xml:space="preserve">Any specifically defined piece of work that is undertaken or attempted to meet the goals of a program and that involves one or more case studies. Also known as a Study or Trial. </t>
   </si>
   <si>
+    <t>PROPEL</t>
+  </si>
+  <si>
+    <t>Public Resource of Patient-derived and Expanded Leukemias</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
@@ -569,12 +788,6 @@
     <t>A cancer registry is an information system designed for the collection, storage, and management of data on persons with cancer. An inventory of individuals or samples, usually focused on a specific diagnosis or condition. In some cases, public health laws require collecting information in registries about individuals who have a specific disease or condition. In other cases, individuals provide information about themselves to these registries voluntarily. Thus, a registry contains Individual Clinical Data, but not Individual Research Data.</t>
   </si>
   <si>
-    <t>Data Repository</t>
-  </si>
-  <si>
-    <t>Biomedical data repositories store, organize, validate, archive, preserve, and distribute data, in compliance with the FAIR Data Principles. It is a system for storing multiple research artifacts, provided at least some of the research artifacts contain Individual Research Data. A data repository often contains artifacts from multiple studies. Some data repositories accept research datasets irrespective of the structure of those datasets; other data repositories require all research datasets to conform to a standard reference model.</t>
-  </si>
-  <si>
     <t>Research Dataset</t>
   </si>
   <si>
@@ -638,6 +851,18 @@
     <t>Sequence Read Archive</t>
   </si>
   <si>
+    <t>SRL</t>
+  </si>
+  <si>
+    <t>Specimen Resource Locator</t>
+  </si>
+  <si>
+    <t>STQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spatial Transcriptomics Quantification </t>
+  </si>
+  <si>
     <t>TARGET</t>
   </si>
   <si>
@@ -650,6 +875,18 @@
     <t>The Cancer Imaging Archive</t>
   </si>
   <si>
+    <t>TCPA</t>
+  </si>
+  <si>
+    <t>The Cancer Proteome Atlas</t>
+  </si>
+  <si>
+    <t>TPC-DTC</t>
+  </si>
+  <si>
+    <t>Texas Pediatric Cancer Drug Testing Core</t>
+  </si>
+  <si>
     <t>TSC</t>
   </si>
   <si>
@@ -680,6 +917,12 @@
     <t>Victorian Paediatric Cancer Consortium</t>
   </si>
   <si>
+    <t>WHO</t>
+  </si>
+  <si>
+    <t>World Health Organization</t>
+  </si>
+  <si>
     <t>XA</t>
   </si>
   <si>
@@ -693,256 +936,13 @@
   </si>
   <si>
     <t>https://www.cancer.gov/publications/dictionaries/cancer-terms/def/xenograft</t>
-  </si>
-  <si>
-    <t>Epidemiologic</t>
-  </si>
-  <si>
-    <t>Relating to the study of the distribution and determinants of health-related states or events (including disease) in populations, and the application of this study to the control of diseases and other health problems.</t>
-  </si>
-  <si>
-    <t>Data Element</t>
-  </si>
-  <si>
-    <t>Proband</t>
-  </si>
-  <si>
-    <t>A proband is a person in a family to receive genetic counseling and/or testing for a suspected hereditary risk or diagnosed disease. A proband may or may not be affected with the disease in question. If the value is true, then the case subject may have been diagnosed with the disease under studied. If the value is false, then the case subject is a member of the family of a proband study participant. The proband indicator for the case carries over to a sample taken from a case subject.</t>
-  </si>
-  <si>
-    <t>https://www.cancer.gov/publications/dictionaries/genetics-dictionary/def/proband</t>
-  </si>
-  <si>
-    <t>PPTP</t>
-  </si>
-  <si>
-    <t>Pediatric Preclinical Testing Program</t>
-  </si>
-  <si>
-    <t>DepMap</t>
-  </si>
-  <si>
-    <t>Dependency Map</t>
-  </si>
-  <si>
-    <t>PeCan</t>
-  </si>
-  <si>
-    <t>Pediatric Cancer Knowledge Base</t>
-  </si>
-  <si>
-    <t>CHoP</t>
-  </si>
-  <si>
-    <t>Children's Hospital of Philadelphia</t>
-  </si>
-  <si>
-    <t>CRI iAtlas</t>
-  </si>
-  <si>
-    <t>Cancer Research Institute iAtlas</t>
-  </si>
-  <si>
-    <t>TCPA</t>
-  </si>
-  <si>
-    <t>The Cancer Proteome Atlas</t>
-  </si>
-  <si>
-    <t>Biospecimen</t>
-  </si>
-  <si>
-    <t>A sample of material, such as urine, blood, tissue, cells, DNA, RNA, or protein, from humans, animals, or plants. Biospecimens may be used for a laboratory test or stored in a biorepository to be used for research.</t>
-  </si>
-  <si>
-    <t>https://www.cancer.gov/publications/dictionaries/cancer-terms/def/biospecimen</t>
-  </si>
-  <si>
-    <t>Biorepository</t>
-  </si>
-  <si>
-    <t>A biorepository is a facility that acts as a library for biospecimens, allowing the biospecimens to be available for use in future research. A biospecimen may be from people, animals, or other living organisms. A biorepository will be involved in collecting, cataloguing, and storing biospecimens. The biorepository will also be involved in managing access to and distributing biospecimens to researchers. Some biorepositories store medical information associated with biospecimens.</t>
-  </si>
-  <si>
-    <t>https://toolkit.ncats.nih.gov/glossary/biorepository/</t>
-  </si>
-  <si>
-    <t>NCCB</t>
-  </si>
-  <si>
-    <t>Norwegian Childhood Cancer Biobank</t>
-  </si>
-  <si>
-    <t>BPC</t>
-  </si>
-  <si>
-    <t>The Biopathology Center</t>
-  </si>
-  <si>
-    <t>BTB</t>
-  </si>
-  <si>
-    <t>Swedish Childhood Tumor Biobank (Barntumörbanken)</t>
-  </si>
-  <si>
-    <t>IDC</t>
-  </si>
-  <si>
-    <t>Imaging Data Commons</t>
-  </si>
-  <si>
-    <t>OSE</t>
-  </si>
-  <si>
-    <t>Osteosarcoma Explorer</t>
-  </si>
-  <si>
-    <t>PROPEL</t>
-  </si>
-  <si>
-    <t>Public Resource of Patient-derived and Expanded Leukemias</t>
-  </si>
-  <si>
-    <t>ITCC P4</t>
-  </si>
-  <si>
-    <t>Innovative Therapies for Children with Cancer Paediatric Preclinical Proof-of-Concept Platform</t>
-  </si>
-  <si>
-    <t>NCTN</t>
-  </si>
-  <si>
-    <t>National Clinical Trials Network</t>
-  </si>
-  <si>
-    <t>CEDCD</t>
-  </si>
-  <si>
-    <t>Cancer Epidemiology Descriptive Cohort Database</t>
-  </si>
-  <si>
-    <t>TPC-DTC</t>
-  </si>
-  <si>
-    <t>Texas Pediatric Cancer Drug Testing Core</t>
-  </si>
-  <si>
-    <t>PIVOT</t>
-  </si>
-  <si>
-    <t>Pediatric Preclinical In Vivo Testing Consortium</t>
-  </si>
-  <si>
-    <t>GENIE</t>
-  </si>
-  <si>
-    <t>Genomics Evidence Neoplasia Information Exchange</t>
-  </si>
-  <si>
-    <t>WHO</t>
-  </si>
-  <si>
-    <t>World Health Organization</t>
-  </si>
-  <si>
-    <t>IARC</t>
-  </si>
-  <si>
-    <t>International Agency for Research on Cancer</t>
-  </si>
-  <si>
-    <t>IICC</t>
-  </si>
-  <si>
-    <t>International Incidence of Childhood Cancer</t>
-  </si>
-  <si>
-    <t>ACCIS</t>
-  </si>
-  <si>
-    <t>Automated Childhood Cancer Information System</t>
-  </si>
-  <si>
-    <t>NORDCAN</t>
-  </si>
-  <si>
-    <t>Association of the Nordic Cancer Registries</t>
-  </si>
-  <si>
-    <t>NICD</t>
-  </si>
-  <si>
-    <t>National Institute for Communicable Diseases</t>
-  </si>
-  <si>
-    <t>SRL</t>
-  </si>
-  <si>
-    <t>Specimen Resource Locator</t>
-  </si>
-  <si>
-    <t>DCEG</t>
-  </si>
-  <si>
-    <t>Division of Cancer Epidemiology &amp; Genetics</t>
-  </si>
-  <si>
-    <t>ecDNA</t>
-  </si>
-  <si>
-    <t>Circular Extrachromosomal DNA</t>
-  </si>
-  <si>
-    <t>FAPTP</t>
-  </si>
-  <si>
-    <t>Florida Association of Pediatric Tumor Programs</t>
-  </si>
-  <si>
-    <t>NF-OSI</t>
-  </si>
-  <si>
-    <t>caDSR</t>
-  </si>
-  <si>
-    <t>Cancer Data Standards Registry and Repository</t>
-  </si>
-  <si>
-    <t>FrESCO</t>
-  </si>
-  <si>
-    <t>Framework for Exploring Scalable Computational Oncology</t>
-  </si>
-  <si>
-    <t>PMTL</t>
-  </si>
-  <si>
-    <t>Pediatric Molecular Target Lists</t>
-  </si>
-  <si>
-    <t>STQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spatial Transcriptomics Quantification </t>
-  </si>
-  <si>
-    <t>Batch-processing Abstraction for Raw Data Integration</t>
-  </si>
-  <si>
-    <t>BARDI</t>
-  </si>
-  <si>
-    <t>Clinical Interpretation of Variants in Cancer</t>
-  </si>
-  <si>
-    <t>Neurofibromatosis Data Portal Open Science Initiative</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1062,7 +1062,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1091,10 +1091,17 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1114,9 +1121,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1154,7 +1161,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1260,7 +1267,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1402,7 +1409,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1411,16 +1418,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69208F35-5666-473F-97EF-CB7A96B85984}">
   <dimension ref="A1:E135"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="36.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="97.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="97.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1437,115 +1444,121 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="29.1">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="43.5">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
         <v>13</v>
       </c>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="29.1">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="130.5">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="57.95">
+      <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="E8" t="s">
+      <c r="B9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -1554,9 +1567,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
@@ -1565,31 +1578,31 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="29.1">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
         <v>40</v>
@@ -1597,77 +1610,71 @@
       <c r="C14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D14" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="130.5">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
         <v>54</v>
@@ -1676,9 +1683,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B21" t="s">
         <v>56</v>
@@ -1687,489 +1694,495 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="29.1">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C23" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C24" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="29.1">
       <c r="A28" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="C28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C30" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="87">
       <c r="A31" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C31" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>20</v>
-      </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="57.95">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="130.5">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>92</v>
+        <v>5</v>
+      </c>
+      <c r="B38" t="s">
+        <v>94</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" t="s">
-        <v>98</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="43.5">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D42" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E42" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+      <c r="C43" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="57.95">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D45" t="s">
-        <v>109</v>
-      </c>
-      <c r="E45" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>17</v>
-      </c>
-      <c r="B46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" t="s">
         <v>113</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" t="s">
         <v>115</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C48" s="1" t="s">
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="C49" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C49" s="1" t="s">
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>60</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="C50" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C50" t="s">
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>17</v>
-      </c>
-      <c r="B51" s="5" t="s">
+      <c r="C51" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C51" s="1" t="s">
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>17</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="C52" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C52" s="1" t="s">
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>17</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="C53" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C53" s="1" t="s">
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>17</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="C54" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C54" s="1" t="s">
+    </row>
+    <row r="55" spans="1:5" ht="29.1">
+      <c r="A55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>20</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="C55" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C55" s="1" t="s">
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>20</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="C56" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C56" s="1" t="s">
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="C57" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="1" t="s">
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>20</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="C58" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C58" s="1" t="s">
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>17</v>
-      </c>
-      <c r="B59" s="4" t="s">
+      <c r="C59" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C59" s="5" t="s">
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>17</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="C60" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C60" s="1" t="s">
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" t="s">
+      <c r="C61" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C61" s="1" t="s">
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" s="12" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>17</v>
-      </c>
-      <c r="B62" t="s">
+      <c r="C62" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="C62" s="1" t="s">
+    </row>
+    <row r="63" spans="1:5" ht="43.5">
+      <c r="A63" t="s">
+        <v>27</v>
+      </c>
+      <c r="B63" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>17</v>
-      </c>
-      <c r="B63" t="s">
+      <c r="C63" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" ht="29.1">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B64" t="s">
         <v>148</v>
@@ -2178,9 +2191,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B65" t="s">
         <v>150</v>
@@ -2189,9 +2202,9 @@
         <v>151</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B66" t="s">
         <v>152</v>
@@ -2200,379 +2213,367 @@
         <v>153</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="43.5">
       <c r="A67" t="s">
-        <v>17</v>
-      </c>
-      <c r="B67" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" t="s">
         <v>154</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C67" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D67" t="s">
+        <v>156</v>
+      </c>
+      <c r="E67" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B68" t="s">
-        <v>156</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>158</v>
+      </c>
+      <c r="C68" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>115</v>
-      </c>
-      <c r="B69" t="s">
-        <v>158</v>
+        <v>5</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="29.1">
       <c r="A70" t="s">
-        <v>17</v>
+        <v>162</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B71" t="s">
+        <v>165</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>81</v>
+      </c>
+      <c r="B72" t="s">
+        <v>167</v>
+      </c>
+      <c r="C72" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>5</v>
+      </c>
+      <c r="B74" t="s">
+        <v>171</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" t="s">
+        <v>173</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" t="s">
+        <v>175</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>5</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>37</v>
+      </c>
+      <c r="B78" t="s">
+        <v>179</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>5</v>
+      </c>
+      <c r="B79" t="s">
+        <v>181</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>5</v>
+      </c>
+      <c r="B81" t="s">
+        <v>185</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>37</v>
+      </c>
+      <c r="B82" t="s">
+        <v>187</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>81</v>
+      </c>
+      <c r="B83" t="s">
+        <v>189</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>5</v>
+      </c>
+      <c r="B84" t="s">
+        <v>191</v>
+      </c>
+      <c r="C84" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>37</v>
+      </c>
+      <c r="B85" t="s">
+        <v>193</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>5</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>5</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>5</v>
+      </c>
+      <c r="B88" t="s">
+        <v>199</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B89" t="s">
+        <v>201</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>5</v>
+      </c>
+      <c r="B90" t="s">
+        <v>203</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91" t="s">
+        <v>205</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" t="s">
+        <v>207</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>37</v>
+      </c>
+      <c r="B93" t="s">
+        <v>209</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" t="s">
+        <v>211</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" t="s">
+        <v>213</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>5</v>
+      </c>
+      <c r="B97" t="s">
+        <v>217</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="29.1">
+      <c r="A98" t="s">
         <v>162</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="87" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>164</v>
-      </c>
-      <c r="B72" t="s">
-        <v>5</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>166</v>
-      </c>
-      <c r="B73" t="s">
-        <v>167</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>166</v>
-      </c>
-      <c r="B74" t="s">
-        <v>169</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>60</v>
-      </c>
-      <c r="B75" t="s">
-        <v>171</v>
-      </c>
-      <c r="C75" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>164</v>
-      </c>
-      <c r="B76" t="s">
-        <v>3</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="145" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>10</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>10</v>
-      </c>
-      <c r="B78" t="s">
-        <v>176</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>164</v>
-      </c>
-      <c r="B79" t="s">
-        <v>178</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D79" t="s">
-        <v>8</v>
-      </c>
-      <c r="E79" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>67</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>17</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>60</v>
-      </c>
-      <c r="B82" t="s">
-        <v>184</v>
-      </c>
-      <c r="C82" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>60</v>
-      </c>
-      <c r="B83" t="s">
-        <v>186</v>
-      </c>
-      <c r="C83" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="116" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>5</v>
-      </c>
-      <c r="B84" t="s">
-        <v>188</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D84" t="s">
-        <v>8</v>
-      </c>
-      <c r="E84" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>60</v>
-      </c>
-      <c r="B85" t="s">
-        <v>191</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>17</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>17</v>
-      </c>
-      <c r="B87" t="s">
-        <v>195</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>17</v>
-      </c>
-      <c r="B88" t="s">
-        <v>197</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>17</v>
-      </c>
-      <c r="B89" t="s">
-        <v>199</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>17</v>
-      </c>
-      <c r="B90" t="s">
-        <v>201</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>17</v>
-      </c>
-      <c r="B91" t="s">
-        <v>203</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>17</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>60</v>
-      </c>
-      <c r="B93" t="s">
-        <v>207</v>
-      </c>
-      <c r="C93" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>20</v>
-      </c>
-      <c r="B94" t="s">
-        <v>209</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>17</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>60</v>
-      </c>
-      <c r="B96" t="s">
-        <v>213</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>39</v>
-      </c>
-      <c r="B97" t="s">
-        <v>215</v>
-      </c>
-      <c r="C97" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="D97" t="s">
-        <v>15</v>
-      </c>
-      <c r="E97" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>50</v>
-      </c>
       <c r="B98" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>220</v>
+        <v>5</v>
       </c>
       <c r="B99" t="s">
         <v>221</v>
@@ -2580,71 +2581,65 @@
       <c r="C99" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D99" t="s">
-        <v>15</v>
-      </c>
-      <c r="E99" s="11" t="s">
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>5</v>
+      </c>
+      <c r="B100" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>17</v>
-      </c>
-      <c r="B100" t="s">
+      <c r="C100" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C100" s="8" t="s">
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>5</v>
+      </c>
+      <c r="B101" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>17</v>
-      </c>
-      <c r="B101" t="s">
+      <c r="C101" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C101" s="1" t="s">
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>5</v>
+      </c>
+      <c r="B102" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>17</v>
-      </c>
-      <c r="B102" t="s">
+      <c r="C102" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C102" s="1" t="s">
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>5</v>
+      </c>
+      <c r="B103" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>20</v>
-      </c>
-      <c r="B103" t="s">
+      <c r="C103" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="C103" s="1" t="s">
+    </row>
+    <row r="104" spans="1:5" ht="87">
+      <c r="A104" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>17</v>
-      </c>
       <c r="B104" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C104" s="1" t="s">
+    </row>
+    <row r="105" spans="1:5" ht="130.5">
+      <c r="A105" t="s">
         <v>233</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>17</v>
       </c>
       <c r="B105" t="s">
         <v>234</v>
@@ -2652,44 +2647,38 @@
       <c r="C105" s="1" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="D105" t="s">
+        <v>18</v>
+      </c>
+      <c r="E105" s="11" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="72.599999999999994">
       <c r="A106" t="s">
-        <v>50</v>
+        <v>237</v>
       </c>
       <c r="B106" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C106" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="43.5">
+      <c r="A107" t="s">
         <v>237</v>
       </c>
-      <c r="D106" t="s">
-        <v>15</v>
-      </c>
-      <c r="E106" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>10</v>
-      </c>
       <c r="B107" t="s">
-        <v>239</v>
-      </c>
-      <c r="C107" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D107" t="s">
-        <v>15</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="C107" s="4" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B108" t="s">
         <v>242</v>
@@ -2698,108 +2687,120 @@
         <v>243</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="B109" t="s">
         <v>244</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C109" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" ht="43.5">
       <c r="A110" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="B110" t="s">
+        <v>3</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C110" s="1" t="s">
+    </row>
+    <row r="111" spans="1:5" ht="144.94999999999999">
+      <c r="A111" t="s">
+        <v>13</v>
+      </c>
+      <c r="B111" s="14" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>17</v>
-      </c>
-      <c r="B111" t="s">
+      <c r="C111" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="C111" s="1" t="s">
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>231</v>
+      </c>
+      <c r="B112" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>17</v>
-      </c>
-      <c r="B112" t="s">
+      <c r="C112" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" ht="43.5">
       <c r="A113" t="s">
-        <v>17</v>
-      </c>
-      <c r="B113" t="s">
+        <v>90</v>
+      </c>
+      <c r="B113" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="C113" s="1" t="s">
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>5</v>
+      </c>
+      <c r="B114" s="5" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B114" t="s">
+      <c r="C114" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="C114" s="1" t="s">
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>81</v>
+      </c>
+      <c r="B115" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>17</v>
-      </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>256</v>
       </c>
-      <c r="C115" s="1" t="s">
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>81</v>
+      </c>
+      <c r="B116" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>17</v>
-      </c>
-      <c r="B116" t="s">
+      <c r="C116" t="s">
         <v>258</v>
       </c>
-      <c r="C116" s="1" t="s">
+    </row>
+    <row r="117" spans="1:5" ht="116.1">
+      <c r="A117" t="s">
+        <v>8</v>
+      </c>
+      <c r="B117" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>17</v>
-      </c>
-      <c r="B117" t="s">
+      <c r="C117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="B118" t="s">
         <v>262</v>
@@ -2808,20 +2809,20 @@
         <v>263</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>17</v>
-      </c>
-      <c r="B119" t="s">
+        <v>5</v>
+      </c>
+      <c r="B119" s="5" t="s">
         <v>264</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B120" t="s">
         <v>266</v>
@@ -2830,9 +2831,9 @@
         <v>267</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B121" t="s">
         <v>268</v>
@@ -2841,42 +2842,42 @@
         <v>269</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>17</v>
-      </c>
-      <c r="B122" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B122" t="s">
         <v>270</v>
       </c>
-      <c r="C122" s="12" t="s">
+      <c r="C122" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>17</v>
-      </c>
-      <c r="B123" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B123" t="s">
         <v>272</v>
       </c>
-      <c r="C123" s="13" t="s">
+      <c r="C123" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" ht="29.1">
       <c r="A124" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B124" t="s">
         <v>274</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B125" t="s">
         <v>276</v>
@@ -2885,9 +2886,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B126" t="s">
         <v>278</v>
@@ -2896,9 +2897,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B127" t="s">
         <v>280</v>
@@ -2907,9 +2908,9 @@
         <v>281</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B128" t="s">
         <v>282</v>
@@ -2918,91 +2919,97 @@
         <v>283</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>17</v>
-      </c>
-      <c r="B129" t="s">
+        <v>5</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>284</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="B130" t="s">
         <v>286</v>
       </c>
-      <c r="C130" s="14" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C130" s="7" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B131" t="s">
-        <v>287</v>
-      </c>
-      <c r="C131" s="15" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C131" s="16" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>17</v>
-      </c>
-      <c r="B132" t="s">
-        <v>289</v>
-      </c>
-      <c r="C132" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B132" s="5" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C132" s="16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B133" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="B134" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="29.1">
       <c r="A135" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="B135" t="s">
         <v>296</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>295</v>
+      <c r="C135" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="D135" t="s">
+        <v>18</v>
+      </c>
+      <c r="E135" t="s">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Z93" xr:uid="{A4DAB4A1-0C2C-4B2F-A024-FF4C6E1E16D8}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E97">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E135">
       <sortCondition ref="B1:B93"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="E99" r:id="rId1" xr:uid="{D3DBCC56-4DE9-4D48-A14F-C1E905DF0FDE}"/>
+    <hyperlink ref="E105" r:id="rId1" xr:uid="{D3DBCC56-4DE9-4D48-A14F-C1E905DF0FDE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
@@ -3277,45 +3284,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{408CD603-C2F6-45F8-91C0-1EC5F05A3CA2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="00850a8a-55a0-4f29-bb56-d3de9b9bc75c"/>
-    <ds:schemaRef ds:uri="33e70369-3675-4c3b-99e1-030eb9633bdf"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{408CD603-C2F6-45F8-91C0-1EC5F05A3CA2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13521947-7B63-4043-9A52-D2F3EDCA31C1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="33e70369-3675-4c3b-99e1-030eb9633bdf"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="00850a8a-55a0-4f29-bb56-d3de9b9bc75c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13521947-7B63-4043-9A52-D2F3EDCA31C1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7554B1E-EA5B-4036-8BEB-CEB54DFFA990}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7554B1E-EA5B-4036-8BEB-CEB54DFFA990}"/>
 </file>